--- a/Outputs/Recycling_Plot_Data/Repeal/03_National_Timeseries_data_Repeal.xlsx
+++ b/Outputs/Recycling_Plot_Data/Repeal/03_National_Timeseries_data_Repeal.xlsx
@@ -401,7 +401,7 @@
         </is>
       </c>
       <c r="E2">
-        <v>1.223911541752326</v>
+        <v>1.048112885751661</v>
       </c>
     </row>
     <row r="3">
@@ -424,7 +424,7 @@
         </is>
       </c>
       <c r="E3">
-        <v>1.156077799694751</v>
+        <v>0.990230768645939</v>
       </c>
     </row>
     <row r="4">
@@ -493,7 +493,7 @@
         </is>
       </c>
       <c r="E6">
-        <v>0.7358595268247212</v>
+        <v>0.6274956291952201</v>
       </c>
     </row>
     <row r="7">
@@ -516,7 +516,7 @@
         </is>
       </c>
       <c r="E7">
-        <v>0.6948840702975244</v>
+        <v>0.592654445204929</v>
       </c>
     </row>
     <row r="8">
@@ -631,7 +631,7 @@
         </is>
       </c>
       <c r="E12">
-        <v>1.239289575443776</v>
+        <v>1.239187482648495</v>
       </c>
     </row>
     <row r="13">
@@ -654,7 +654,7 @@
         </is>
       </c>
       <c r="E13">
-        <v>1.110406170487691</v>
+        <v>1.110315126856621</v>
       </c>
     </row>
     <row r="14">
@@ -723,7 +723,7 @@
         </is>
       </c>
       <c r="E16">
-        <v>0.7454706603244939</v>
+        <v>0.7454074741223253</v>
       </c>
     </row>
     <row r="17">
@@ -746,7 +746,7 @@
         </is>
       </c>
       <c r="E17">
-        <v>0.6675792841435657</v>
+        <v>0.6675229363742345</v>
       </c>
     </row>
     <row r="18">
@@ -769,7 +769,7 @@
         </is>
       </c>
       <c r="E18">
-        <v>0.008757882634927008</v>
+        <v>0.008640537652918079</v>
       </c>
     </row>
     <row r="19">
@@ -792,7 +792,7 @@
         </is>
       </c>
       <c r="E19">
-        <v>0.008658081031664315</v>
+        <v>0.008544273976468036</v>
       </c>
     </row>
     <row r="20">
@@ -861,7 +861,7 @@
         </is>
       </c>
       <c r="E22">
-        <v>1.639972616235561</v>
+        <v>1.639803256109568</v>
       </c>
     </row>
     <row r="23">
@@ -884,7 +884,7 @@
         </is>
       </c>
       <c r="E23">
-        <v>1.393992194382935</v>
+        <v>1.393849072541781</v>
       </c>
     </row>
     <row r="24">
@@ -999,7 +999,7 @@
         </is>
       </c>
       <c r="E28">
-        <v>0.01771908114111269</v>
+        <v>0.01753696444387591</v>
       </c>
     </row>
     <row r="29">
@@ -1022,7 +1022,7 @@
         </is>
       </c>
       <c r="E29">
-        <v>0.01723063643670869</v>
+        <v>0.01705399849234609</v>
       </c>
     </row>
     <row r="30">
@@ -1091,7 +1091,7 @@
         </is>
       </c>
       <c r="E32">
-        <v>2.13614833275339</v>
+        <v>2.135866434087277</v>
       </c>
     </row>
     <row r="33">
@@ -1114,7 +1114,7 @@
         </is>
       </c>
       <c r="E33">
-        <v>1.725424598589868</v>
+        <v>1.7251985901789</v>
       </c>
     </row>
     <row r="34">
@@ -1229,7 +1229,7 @@
         </is>
       </c>
       <c r="E38">
-        <v>0.03087789986919427</v>
+        <v>0.03059017004747618</v>
       </c>
     </row>
     <row r="39">
@@ -1252,7 +1252,7 @@
         </is>
       </c>
       <c r="E39">
-        <v>0.0296413690615514</v>
+        <v>0.02936226135524145</v>
       </c>
     </row>
     <row r="40">
@@ -1321,7 +1321,7 @@
         </is>
       </c>
       <c r="E42">
-        <v>2.64703591232124</v>
+        <v>2.646565972984522</v>
       </c>
     </row>
     <row r="43">
@@ -1344,7 +1344,7 @@
         </is>
       </c>
       <c r="E43">
-        <v>2.034099852454536</v>
+        <v>2.033741524549251</v>
       </c>
     </row>
     <row r="44">
@@ -1459,7 +1459,7 @@
         </is>
       </c>
       <c r="E48">
-        <v>0.05056054629543626</v>
+        <v>0.05011094743356139</v>
       </c>
     </row>
     <row r="49">
@@ -1482,7 +1482,7 @@
         </is>
       </c>
       <c r="E49">
-        <v>0.04792165341202376</v>
+        <v>0.04748552575662294</v>
       </c>
     </row>
     <row r="50">
@@ -1551,7 +1551,7 @@
         </is>
       </c>
       <c r="E52">
-        <v>3.22767657276408</v>
+        <v>3.226897538852309</v>
       </c>
     </row>
     <row r="53">
@@ -1574,7 +1574,7 @@
         </is>
       </c>
       <c r="E53">
-        <v>2.36341435536712</v>
+        <v>2.362849142981503</v>
       </c>
     </row>
     <row r="54">
@@ -1689,7 +1689,7 @@
         </is>
       </c>
       <c r="E58">
-        <v>0.07891089528030837</v>
+        <v>0.07820327653423326</v>
       </c>
     </row>
     <row r="59">
@@ -1712,7 +1712,7 @@
         </is>
       </c>
       <c r="E59">
-        <v>0.07380625485292677</v>
+        <v>0.07311963020992929</v>
       </c>
     </row>
     <row r="60">
@@ -1781,7 +1781,7 @@
         </is>
       </c>
       <c r="E62">
-        <v>3.884171274796751</v>
+        <v>3.882881276944692</v>
       </c>
     </row>
     <row r="63">
@@ -1804,7 +1804,7 @@
         </is>
       </c>
       <c r="E63">
-        <v>2.716062883904863</v>
+        <v>2.71516994539702</v>
       </c>
     </row>
     <row r="64">
@@ -1919,7 +1919,7 @@
         </is>
       </c>
       <c r="E68">
-        <v>0.1204593419346942</v>
+        <v>0.1193549313294477</v>
       </c>
     </row>
     <row r="69">
@@ -1942,7 +1942,7 @@
         </is>
       </c>
       <c r="E69">
-        <v>0.1113911320077479</v>
+        <v>0.1103199689003173</v>
       </c>
     </row>
     <row r="70">
@@ -2011,7 +2011,7 @@
         </is>
       </c>
       <c r="E72">
-        <v>4.589995940491145</v>
+        <v>4.587895927590325</v>
       </c>
     </row>
     <row r="73">
@@ -2034,7 +2034,7 @@
         </is>
       </c>
       <c r="E73">
-        <v>3.065908295863664</v>
+        <v>3.064520916377869</v>
       </c>
     </row>
     <row r="74">
@@ -2103,7 +2103,7 @@
         </is>
       </c>
       <c r="E76">
-        <v>2.803925670036546</v>
+        <v>2.802602953218782</v>
       </c>
     </row>
     <row r="77">
@@ -2149,7 +2149,7 @@
         </is>
       </c>
       <c r="E78">
-        <v>0.174286894039772</v>
+        <v>0.1725743031682744</v>
       </c>
     </row>
     <row r="79">
@@ -2172,7 +2172,7 @@
         </is>
       </c>
       <c r="E79">
-        <v>0.1590738961560312</v>
+        <v>0.1574124665094089</v>
       </c>
     </row>
     <row r="80">
@@ -2241,7 +2241,7 @@
         </is>
       </c>
       <c r="E82">
-        <v>5.454762968655211</v>
+        <v>5.451381878153582</v>
       </c>
     </row>
     <row r="83">
@@ -2264,7 +2264,7 @@
         </is>
       </c>
       <c r="E83">
-        <v>3.47610773514843</v>
+        <v>3.473977176161767</v>
       </c>
     </row>
     <row r="84">
@@ -2333,7 +2333,7 @@
         </is>
       </c>
       <c r="E86">
-        <v>3.347039030972701</v>
+        <v>3.344906282045755</v>
       </c>
     </row>
     <row r="87">
@@ -2379,7 +2379,7 @@
         </is>
       </c>
       <c r="E88">
-        <v>0.2427893195463904</v>
+        <v>0.2401835596369448</v>
       </c>
     </row>
     <row r="89">
@@ -2402,7 +2402,7 @@
         </is>
       </c>
       <c r="E89">
-        <v>0.218290594784227</v>
+        <v>0.2157638907995428</v>
       </c>
     </row>
     <row r="90">
@@ -2471,7 +2471,7 @@
         </is>
       </c>
       <c r="E92">
-        <v>6.058155209728583</v>
+        <v>6.052790268229301</v>
       </c>
     </row>
     <row r="93">
@@ -2494,7 +2494,7 @@
         </is>
       </c>
       <c r="E93">
-        <v>3.689692712423453</v>
+        <v>3.686458362747367</v>
       </c>
     </row>
     <row r="94">
@@ -2517,7 +2517,7 @@
         </is>
       </c>
       <c r="E94">
-        <v>5.903511797306224</v>
+        <v>5.898144443686063</v>
       </c>
     </row>
     <row r="95">
@@ -2563,7 +2563,7 @@
         </is>
       </c>
       <c r="E96">
-        <v>3.726889050659104</v>
+        <v>3.723500638452133</v>
       </c>
     </row>
     <row r="97">
@@ -2609,7 +2609,7 @@
         </is>
       </c>
       <c r="E98">
-        <v>0.3334736612621502</v>
+        <v>0.3294941318471499</v>
       </c>
     </row>
     <row r="99">
@@ -2632,7 +2632,7 @@
         </is>
       </c>
       <c r="E99">
-        <v>0.2955353653669405</v>
+        <v>0.2916786188369913</v>
       </c>
     </row>
     <row r="100">
@@ -2701,7 +2701,7 @@
         </is>
       </c>
       <c r="E102">
-        <v>6.694900807239724</v>
+        <v>6.686567876012948</v>
       </c>
     </row>
     <row r="103">
@@ -2724,7 +2724,7 @@
         </is>
       </c>
       <c r="E103">
-        <v>3.903282230786212</v>
+        <v>3.898461526452732</v>
       </c>
     </row>
     <row r="104">
@@ -2747,7 +2747,7 @@
         </is>
       </c>
       <c r="E104">
-        <v>6.531873669555792</v>
+        <v>6.523529140989499</v>
       </c>
     </row>
     <row r="105">
@@ -2793,7 +2793,7 @@
         </is>
       </c>
       <c r="E106">
-        <v>4.123574119130918</v>
+        <v>4.118306215345103</v>
       </c>
     </row>
     <row r="107">
@@ -2839,7 +2839,7 @@
         </is>
       </c>
       <c r="E108">
-        <v>0.4527213109388475</v>
+        <v>0.4466797534244165</v>
       </c>
     </row>
     <row r="109">
@@ -2862,7 +2862,7 @@
         </is>
       </c>
       <c r="E109">
-        <v>0.3963173014230557</v>
+        <v>0.3904677024049901</v>
       </c>
     </row>
     <row r="110">
@@ -2931,7 +2931,7 @@
         </is>
       </c>
       <c r="E112">
-        <v>7.07697557233826</v>
+        <v>7.064946620232408</v>
       </c>
     </row>
     <row r="113">
@@ -2954,7 +2954,7 @@
         </is>
       </c>
       <c r="E113">
-        <v>4.077689082364879</v>
+        <v>4.070803045340762</v>
       </c>
     </row>
     <row r="114">
@@ -2977,7 +2977,7 @@
         </is>
       </c>
       <c r="E114">
-        <v>6.909422955469076</v>
+        <v>6.897378931643952</v>
       </c>
     </row>
     <row r="115">
@@ -3023,7 +3023,7 @@
         </is>
       </c>
       <c r="E116">
-        <v>4.361921114625436</v>
+        <v>4.354317718196177</v>
       </c>
     </row>
     <row r="117">
@@ -3069,7 +3069,7 @@
         </is>
       </c>
       <c r="E118">
-        <v>0.6041747913381367</v>
+        <v>0.5953644460410641</v>
       </c>
     </row>
     <row r="119">
@@ -3092,7 +3092,7 @@
         </is>
       </c>
       <c r="E119">
-        <v>0.5229524356582044</v>
+        <v>0.5144358095385773</v>
       </c>
     </row>
     <row r="120">
@@ -3161,7 +3161,7 @@
         </is>
       </c>
       <c r="E122">
-        <v>7.415658706089365</v>
+        <v>7.404895482811019</v>
       </c>
     </row>
     <row r="123">
@@ -3184,7 +3184,7 @@
         </is>
       </c>
       <c r="E123">
-        <v>4.222317007606567</v>
+        <v>4.21622506156321</v>
       </c>
     </row>
     <row r="124">
@@ -3207,7 +3207,7 @@
         </is>
       </c>
       <c r="E124">
-        <v>7.241360235008122</v>
+        <v>7.230592395832873</v>
       </c>
     </row>
     <row r="125">
@@ -3253,7 +3253,7 @@
         </is>
       </c>
       <c r="E126">
-        <v>4.571473234633754</v>
+        <v>4.564675494017769</v>
       </c>
     </row>
     <row r="127">
@@ -3299,7 +3299,7 @@
         </is>
       </c>
       <c r="E128">
-        <v>0.7845754219269226</v>
+        <v>0.772164957930041</v>
       </c>
     </row>
     <row r="129">
@@ -3322,7 +3322,7 @@
         </is>
       </c>
       <c r="E129">
-        <v>0.6709141016465038</v>
+        <v>0.6589457942876035</v>
       </c>
     </row>
     <row r="130">
@@ -3391,7 +3391,7 @@
         </is>
       </c>
       <c r="E132">
-        <v>7.737110674077925</v>
+        <v>7.718296245142723</v>
       </c>
     </row>
     <row r="133">
@@ -3414,7 +3414,7 @@
         </is>
       </c>
       <c r="E133">
-        <v>4.354411859392259</v>
+        <v>4.343868948500009</v>
       </c>
     </row>
     <row r="134">
@@ -3437,7 +3437,7 @@
         </is>
       </c>
       <c r="E134">
-        <v>7.555136640296787</v>
+        <v>7.536330777180381</v>
       </c>
     </row>
     <row r="135">
@@ -3483,7 +3483,7 @@
         </is>
       </c>
       <c r="E136">
-        <v>4.769560388412138</v>
+        <v>4.757688240486775</v>
       </c>
     </row>
     <row r="137">
@@ -3506,7 +3506,7 @@
         </is>
       </c>
       <c r="E137">
-        <v>2.678364910016596</v>
+        <v>2.671712196925607</v>
       </c>
     </row>
     <row r="138">
@@ -3529,7 +3529,7 @@
         </is>
       </c>
       <c r="E138">
-        <v>1.05042874399325</v>
+        <v>1.01471697093446</v>
       </c>
     </row>
     <row r="139">
@@ -3552,7 +3552,7 @@
         </is>
       </c>
       <c r="E139">
-        <v>0.8919167792310266</v>
+        <v>0.8573805002601222</v>
       </c>
     </row>
     <row r="140">
@@ -3621,7 +3621,7 @@
         </is>
       </c>
       <c r="E142">
-        <v>8.040161417368774</v>
+        <v>8.017665737881861</v>
       </c>
     </row>
     <row r="143">
@@ -3644,7 +3644,7 @@
         </is>
       </c>
       <c r="E143">
-        <v>4.473719557499303</v>
+        <v>4.461253017638732</v>
       </c>
     </row>
     <row r="144">
@@ -3667,7 +3667,7 @@
         </is>
       </c>
       <c r="E144">
-        <v>7.846028838561796</v>
+        <v>7.823575934987065</v>
       </c>
     </row>
     <row r="145">
@@ -3713,7 +3713,7 @@
         </is>
       </c>
       <c r="E146">
-        <v>4.953200734338219</v>
+        <v>4.939026208503215</v>
       </c>
     </row>
     <row r="147">
@@ -3736,7 +3736,7 @@
         </is>
       </c>
       <c r="E147">
-        <v>2.75016230463818</v>
+        <v>2.742307138874923</v>
       </c>
     </row>
     <row r="148">
@@ -3759,7 +3759,7 @@
         </is>
       </c>
       <c r="E148">
-        <v>1.28609692839741</v>
+        <v>1.24449217584713</v>
       </c>
     </row>
     <row r="149">
@@ -3782,7 +3782,7 @@
         </is>
       </c>
       <c r="E149">
-        <v>1.068950252870806</v>
+        <v>1.028746002274721</v>
       </c>
     </row>
     <row r="150">
@@ -3851,7 +3851,7 @@
         </is>
       </c>
       <c r="E152">
-        <v>8.30644598771053</v>
+        <v>8.282415390255133</v>
       </c>
     </row>
     <row r="153">
@@ -3874,7 +3874,7 @@
         </is>
       </c>
       <c r="E153">
-        <v>4.570636587652518</v>
+        <v>4.557466296589561</v>
       </c>
     </row>
     <row r="154">
@@ -3897,7 +3897,7 @@
         </is>
       </c>
       <c r="E154">
-        <v>8.109293314203152</v>
+        <v>8.085308411328253</v>
       </c>
     </row>
     <row r="155">
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="E156">
-        <v>5.119399689364103</v>
+        <v>5.104258011838132</v>
       </c>
     </row>
     <row r="157">
@@ -3966,7 +3966,7 @@
         </is>
       </c>
       <c r="E157">
-        <v>2.811024006522635</v>
+        <v>2.802725407181995</v>
       </c>
     </row>
     <row r="158">
@@ -3989,7 +3989,7 @@
         </is>
       </c>
       <c r="E158">
-        <v>1.542580554414554</v>
+        <v>1.499007542559099</v>
       </c>
     </row>
     <row r="159">
@@ -4012,7 +4012,7 @@
         </is>
       </c>
       <c r="E159">
-        <v>1.248716509693278</v>
+        <v>1.206669351612814</v>
       </c>
     </row>
     <row r="160">
@@ -4081,7 +4081,7 @@
         </is>
       </c>
       <c r="E162">
-        <v>8.465350413514484</v>
+        <v>8.442779786568195</v>
       </c>
     </row>
     <row r="163">
@@ -4104,7 +4104,7 @@
         </is>
       </c>
       <c r="E163">
-        <v>4.658670857538914</v>
+        <v>4.646297988408151</v>
       </c>
     </row>
     <row r="164">
@@ -4127,7 +4127,7 @@
         </is>
       </c>
       <c r="E164">
-        <v>8.265681651746734</v>
+        <v>8.243153943222747</v>
       </c>
     </row>
     <row r="165">
@@ -4173,7 +4173,7 @@
         </is>
       </c>
       <c r="E166">
-        <v>5.218127701241356</v>
+        <v>5.203905951015875</v>
       </c>
     </row>
     <row r="167">
@@ -4196,7 +4196,7 @@
         </is>
       </c>
       <c r="E167">
-        <v>2.865652883070026</v>
+        <v>2.857856739224796</v>
       </c>
     </row>
     <row r="168">
@@ -4219,7 +4219,7 @@
         </is>
       </c>
       <c r="E168">
-        <v>1.821803356478726</v>
+        <v>1.781314960252004</v>
       </c>
     </row>
     <row r="169">
@@ -4242,7 +4242,7 @@
         </is>
       </c>
       <c r="E169">
-        <v>1.429635845039396</v>
+        <v>1.390652264607815</v>
       </c>
     </row>
     <row r="170">
@@ -4311,7 +4311,7 @@
         </is>
       </c>
       <c r="E172">
-        <v>8.716594076876644</v>
+        <v>8.697832181644165</v>
       </c>
     </row>
     <row r="173">
@@ -4334,7 +4334,7 @@
         </is>
       </c>
       <c r="E173">
-        <v>4.796703146661318</v>
+        <v>4.786418593941626</v>
       </c>
     </row>
     <row r="174">
@@ -4357,7 +4357,7 @@
         </is>
       </c>
       <c r="E174">
-        <v>8.514703718750148</v>
+        <v>8.495977499573316</v>
       </c>
     </row>
     <row r="175">
@@ -4403,7 +4403,7 @@
         </is>
       </c>
       <c r="E176">
-        <v>5.375335418741136</v>
+        <v>5.363513550062526</v>
       </c>
     </row>
     <row r="177">
@@ -4426,7 +4426,7 @@
         </is>
       </c>
       <c r="E177">
-        <v>2.951964182637326</v>
+        <v>2.945483886794932</v>
       </c>
     </row>
     <row r="178">
@@ -4449,7 +4449,7 @@
         </is>
       </c>
       <c r="E178">
-        <v>2.131557098167385</v>
+        <v>2.098172274205877</v>
       </c>
     </row>
     <row r="179">
@@ -4472,7 +4472,7 @@
         </is>
       </c>
       <c r="E179">
-        <v>1.616726330865877</v>
+        <v>1.584700042596694</v>
       </c>
     </row>
     <row r="180">
@@ -4541,7 +4541,7 @@
         </is>
       </c>
       <c r="E182">
-        <v>8.973738530562221</v>
+        <v>8.959752248168753</v>
       </c>
     </row>
     <row r="183">
@@ -4564,7 +4564,7 @@
         </is>
       </c>
       <c r="E183">
-        <v>4.937780646584907</v>
+        <v>4.930113497437185</v>
       </c>
     </row>
     <row r="184">
@@ -4587,7 +4587,7 @@
         </is>
       </c>
       <c r="E184">
-        <v>8.769456055401827</v>
+        <v>8.755496368156811</v>
       </c>
     </row>
     <row r="185">
@@ -4633,7 +4633,7 @@
         </is>
       </c>
       <c r="E186">
-        <v>5.536160657462637</v>
+        <v>5.527347902050203</v>
       </c>
     </row>
     <row r="187">
@@ -4656,7 +4656,7 @@
         </is>
       </c>
       <c r="E187">
-        <v>3.040133719595933</v>
+        <v>3.035302649533949</v>
       </c>
     </row>
     <row r="188">
@@ -4679,7 +4679,7 @@
         </is>
       </c>
       <c r="E188">
-        <v>2.483551000188663</v>
+        <v>2.458579624016132</v>
       </c>
     </row>
     <row r="189">
@@ -4702,7 +4702,7 @@
         </is>
       </c>
       <c r="E189">
-        <v>1.819280785022031</v>
+        <v>1.795487087333379</v>
       </c>
     </row>
     <row r="190">
@@ -4771,7 +4771,7 @@
         </is>
       </c>
       <c r="E192">
-        <v>9.23966978920453</v>
+        <v>9.229871825071635</v>
       </c>
     </row>
     <row r="193">
@@ -4794,7 +4794,7 @@
         </is>
       </c>
       <c r="E193">
-        <v>5.08309392744853</v>
+        <v>5.077721313090025</v>
       </c>
     </row>
     <row r="194">
@@ -4817,7 +4817,7 @@
         </is>
       </c>
       <c r="E194">
-        <v>9.033089279087367</v>
+        <v>9.023309945946133</v>
       </c>
     </row>
     <row r="195">
@@ -4863,7 +4863,7 @@
         </is>
       </c>
       <c r="E196">
-        <v>5.702592403257051</v>
+        <v>5.696418706844105</v>
       </c>
     </row>
     <row r="197">
@@ -4886,7 +4886,7 @@
         </is>
       </c>
       <c r="E197">
-        <v>3.131014332963739</v>
+        <v>3.127629049088091</v>
       </c>
     </row>
     <row r="198">
@@ -4909,7 +4909,7 @@
         </is>
       </c>
       <c r="E198">
-        <v>2.885267999274558</v>
+        <v>2.86758294601726</v>
       </c>
     </row>
     <row r="199">
@@ -4932,7 +4932,7 @@
         </is>
       </c>
       <c r="E199">
-        <v>2.043257499218303</v>
+        <v>2.026602953282027</v>
       </c>
     </row>
     <row r="200">
@@ -5001,7 +5001,7 @@
         </is>
       </c>
       <c r="E202">
-        <v>9.49792049679086</v>
+        <v>9.490911791545079</v>
       </c>
     </row>
     <row r="203">
@@ -5024,7 +5024,7 @@
         </is>
       </c>
       <c r="E203">
-        <v>5.223570958592809</v>
+        <v>5.219724129700128</v>
       </c>
     </row>
     <row r="204">
@@ -5047,7 +5047,7 @@
         </is>
       </c>
       <c r="E204">
-        <v>9.289366706750801</v>
+        <v>9.282371328674543</v>
       </c>
     </row>
     <row r="205">
@@ -5093,7 +5093,7 @@
         </is>
       </c>
       <c r="E206">
-        <v>5.864380432464639</v>
+        <v>5.85996424785237</v>
       </c>
     </row>
     <row r="207">
@@ -5116,7 +5116,7 @@
         </is>
       </c>
       <c r="E207">
-        <v>3.218965513282062</v>
+        <v>3.216541626705848</v>
       </c>
     </row>
     <row r="208">
@@ -5139,7 +5139,7 @@
         </is>
       </c>
       <c r="E208">
-        <v>3.338478503616984</v>
+        <v>3.325863727264205</v>
       </c>
     </row>
     <row r="209">
@@ -5162,7 +5162,7 @@
         </is>
       </c>
       <c r="E209">
-        <v>2.289115582513986</v>
+        <v>2.277473091112367</v>
       </c>
     </row>
     <row r="210">
@@ -5231,7 +5231,7 @@
         </is>
       </c>
       <c r="E212">
-        <v>9.771716003315051</v>
+        <v>9.765986030160487</v>
       </c>
     </row>
     <row r="213">
@@ -5254,7 +5254,7 @@
         </is>
       </c>
       <c r="E213">
-        <v>5.37189213473219</v>
+        <v>5.368743625106427</v>
       </c>
     </row>
     <row r="214">
@@ -5277,7 +5277,7 @@
         </is>
       </c>
       <c r="E214">
-        <v>9.561237303451938</v>
+        <v>9.55551822593657</v>
       </c>
     </row>
     <row r="215">
@@ -5323,7 +5323,7 @@
         </is>
       </c>
       <c r="E216">
-        <v>6.03601243470845</v>
+        <v>6.032401979084119</v>
       </c>
     </row>
     <row r="217">
@@ -5346,7 +5346,7 @@
         </is>
       </c>
       <c r="E217">
-        <v>3.311888909306787</v>
+        <v>3.309905033644552</v>
       </c>
     </row>
     <row r="218">
@@ -5369,7 +5369,7 @@
         </is>
       </c>
       <c r="E218">
-        <v>3.849214222123774</v>
+        <v>3.839631745826223</v>
       </c>
     </row>
     <row r="219">
@@ -5392,7 +5392,7 @@
         </is>
       </c>
       <c r="E219">
-        <v>2.558467099010168</v>
+        <v>2.54991668307946</v>
       </c>
     </row>
     <row r="220">
@@ -5461,7 +5461,7 @@
         </is>
       </c>
       <c r="E222">
-        <v>10.01852854687898</v>
+        <v>10.01295067437344</v>
       </c>
     </row>
     <row r="223">
@@ -5484,7 +5484,7 @@
         </is>
       </c>
       <c r="E223">
-        <v>5.505180023972611</v>
+        <v>5.502112029585541</v>
       </c>
     </row>
     <row r="224">
@@ -5507,7 +5507,7 @@
         </is>
       </c>
       <c r="E224">
-        <v>9.806048555192326</v>
+        <v>9.80048128910407</v>
       </c>
     </row>
     <row r="225">
@@ -5553,7 +5553,7 @@
         </is>
       </c>
       <c r="E226">
-        <v>6.19056186306832</v>
+        <v>6.187047246050716</v>
       </c>
     </row>
     <row r="227">
@@ -5576,7 +5576,7 @@
         </is>
       </c>
       <c r="E227">
-        <v>3.395291297545886</v>
+        <v>3.393358154529083</v>
       </c>
     </row>
     <row r="228">
@@ -5599,7 +5599,7 @@
         </is>
       </c>
       <c r="E228">
-        <v>4.392518127578351</v>
+        <v>4.384568121427719</v>
       </c>
     </row>
     <row r="229">
@@ -5622,7 +5622,7 @@
         </is>
       </c>
       <c r="E229">
-        <v>2.833693901598438</v>
+        <v>2.826958015093361</v>
       </c>
     </row>
     <row r="230">
@@ -5691,7 +5691,7 @@
         </is>
       </c>
       <c r="E232">
-        <v>10.25491528212062</v>
+        <v>10.24865020470232</v>
       </c>
     </row>
     <row r="233">
@@ -5714,7 +5714,7 @@
         </is>
       </c>
       <c r="E233">
-        <v>5.632791659082089</v>
+        <v>5.629343809944803</v>
       </c>
     </row>
     <row r="234">
@@ -5737,7 +5737,7 @@
         </is>
       </c>
       <c r="E234">
-        <v>10.03966671134824</v>
+        <v>10.0334135470788</v>
       </c>
     </row>
     <row r="235">
@@ -5760,7 +5760,7 @@
         </is>
       </c>
       <c r="E235">
-        <v>5.504223007517451</v>
+        <v>5.500781714522613</v>
       </c>
     </row>
     <row r="236">
@@ -5783,7 +5783,7 @@
         </is>
       </c>
       <c r="E236">
-        <v>6.338045086293164</v>
+        <v>6.33409746151525</v>
       </c>
     </row>
     <row r="237">
@@ -5806,7 +5806,7 @@
         </is>
       </c>
       <c r="E237">
-        <v>3.474817898807808</v>
+        <v>3.472645409343412</v>
       </c>
     </row>
     <row r="238">
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="E238">
-        <v>4.9535626597187</v>
+        <v>4.946310227283389</v>
       </c>
     </row>
     <row r="239">
@@ -5852,7 +5852,7 @@
         </is>
       </c>
       <c r="E239">
-        <v>3.105513925662542</v>
+        <v>3.099799879554356</v>
       </c>
     </row>
     <row r="240">
@@ -5921,7 +5921,7 @@
         </is>
       </c>
       <c r="E242">
-        <v>10.46549623012226</v>
+        <v>10.45804532212269</v>
       </c>
     </row>
     <row r="243">
@@ -5944,7 +5944,7 @@
         </is>
       </c>
       <c r="E243">
-        <v>5.746039863556021</v>
+        <v>5.741938638767379</v>
       </c>
     </row>
     <row r="244">
@@ -5967,7 +5967,7 @@
         </is>
       </c>
       <c r="E244">
-        <v>10.2478905662319</v>
+        <v>10.24045382625775</v>
       </c>
     </row>
     <row r="245">
@@ -5990,7 +5990,7 @@
         </is>
       </c>
       <c r="E245">
-        <v>5.616077782413632</v>
+        <v>5.611984356172098</v>
       </c>
     </row>
     <row r="246">
@@ -6013,7 +6013,7 @@
         </is>
       </c>
       <c r="E246">
-        <v>6.469496878293663</v>
+        <v>6.464802061761755</v>
       </c>
     </row>
     <row r="247">
@@ -6036,7 +6036,7 @@
         </is>
       </c>
       <c r="E247">
-        <v>3.545431857098656</v>
+        <v>3.542847675688835</v>
       </c>
     </row>
     <row r="248">
@@ -6059,7 +6059,7 @@
         </is>
       </c>
       <c r="E248">
-        <v>5.508083500253681</v>
+        <v>5.50081775685369</v>
       </c>
     </row>
     <row r="249">
@@ -6082,7 +6082,7 @@
         </is>
       </c>
       <c r="E249">
-        <v>3.36763633058031</v>
+        <v>3.362381908340011</v>
       </c>
     </row>
     <row r="250">
@@ -6151,7 +6151,7 @@
         </is>
       </c>
       <c r="E252">
-        <v>10.64882481230261</v>
+        <v>10.63997593461713</v>
       </c>
     </row>
     <row r="253">
@@ -6174,7 +6174,7 @@
         </is>
       </c>
       <c r="E253">
-        <v>5.844789285259726</v>
+        <v>5.839919055361565</v>
       </c>
     </row>
     <row r="254">
@@ -6197,7 +6197,7 @@
         </is>
       </c>
       <c r="E254">
-        <v>10.42808107082273</v>
+        <v>10.41924901942527</v>
       </c>
     </row>
     <row r="255">
@@ -6220,7 +6220,7 @@
         </is>
       </c>
       <c r="E255">
-        <v>5.712959922675694</v>
+        <v>5.708098953600638</v>
       </c>
     </row>
     <row r="256">
@@ -6243,7 +6243,7 @@
         </is>
       </c>
       <c r="E256">
-        <v>6.583251206505342</v>
+        <v>6.577675529386664</v>
       </c>
     </row>
     <row r="257">
@@ -6266,7 +6266,7 @@
         </is>
       </c>
       <c r="E257">
-        <v>3.606593585938066</v>
+        <v>3.603524854470521</v>
       </c>
     </row>
     <row r="258">
@@ -6289,7 +6289,7 @@
         </is>
       </c>
       <c r="E258">
-        <v>6.04188006617848</v>
+        <v>6.03415092062459</v>
       </c>
     </row>
     <row r="259">
@@ -6312,7 +6312,7 @@
         </is>
       </c>
       <c r="E259">
-        <v>3.615577373817797</v>
+        <v>3.610417627631918</v>
       </c>
     </row>
     <row r="260">
